--- a/output/yearly_total_coral_cover_iteration_65_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_65_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.258381072630558</v>
+        <v>1.260491830194688</v>
       </c>
       <c r="C3" t="n">
-        <v>4.627710186710451</v>
+        <v>4.655523099171763</v>
       </c>
       <c r="D3" t="n">
-        <v>6.029506703075372</v>
+        <v>6.136762639764336</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91559796241638</v>
+        <v>12.05277756913079</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.389224453445465</v>
+        <v>1.39971542628037</v>
       </c>
       <c r="C4" t="n">
-        <v>5.106625037638271</v>
+        <v>5.189773612506341</v>
       </c>
       <c r="D4" t="n">
-        <v>6.228488955766571</v>
+        <v>6.494765615580308</v>
       </c>
       <c r="E4" t="n">
-        <v>12.72433844685031</v>
+        <v>13.08425465436702</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.567822276856022</v>
+        <v>1.581422283707176</v>
       </c>
       <c r="C5" t="n">
-        <v>5.715071147482323</v>
+        <v>5.876056195361458</v>
       </c>
       <c r="D5" t="n">
-        <v>6.439774201923794</v>
+        <v>6.904081517466873</v>
       </c>
       <c r="E5" t="n">
-        <v>13.72266762626214</v>
+        <v>14.36155999653551</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.772038669348697</v>
+        <v>1.789226464262463</v>
       </c>
       <c r="C6" t="n">
-        <v>6.459210685495898</v>
+        <v>6.693328845174273</v>
       </c>
       <c r="D6" t="n">
-        <v>6.668998538174205</v>
+        <v>7.273798465883169</v>
       </c>
       <c r="E6" t="n">
-        <v>14.9002478930188</v>
+        <v>15.7563537753199</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.007989556933505</v>
+        <v>2.026038005883567</v>
       </c>
       <c r="C7" t="n">
-        <v>7.306194340566059</v>
+        <v>7.61102783872133</v>
       </c>
       <c r="D7" t="n">
-        <v>6.978481515198051</v>
+        <v>7.713348031550935</v>
       </c>
       <c r="E7" t="n">
-        <v>16.29266541269762</v>
+        <v>17.35041387615583</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.252910882505334</v>
+        <v>1.246807888198828</v>
       </c>
       <c r="C8" t="n">
-        <v>4.900146442457965</v>
+        <v>5.200951611456753</v>
       </c>
       <c r="D8" t="n">
-        <v>5.180762067516663</v>
+        <v>5.95223330032561</v>
       </c>
       <c r="E8" t="n">
-        <v>11.33381939247996</v>
+        <v>12.39999279998119</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.597248719759422</v>
+        <v>1.581970687095269</v>
       </c>
       <c r="C9" t="n">
-        <v>5.954051423068624</v>
+        <v>6.363460991493074</v>
       </c>
       <c r="D9" t="n">
-        <v>5.575945220233567</v>
+        <v>6.495953677582749</v>
       </c>
       <c r="E9" t="n">
-        <v>13.12724536306161</v>
+        <v>14.44138535617109</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.960824211090564</v>
+        <v>1.930079525920942</v>
       </c>
       <c r="C10" t="n">
-        <v>7.150706676112072</v>
+        <v>7.671113641071977</v>
       </c>
       <c r="D10" t="n">
-        <v>5.95959060273529</v>
+        <v>7.020391933895457</v>
       </c>
       <c r="E10" t="n">
-        <v>15.07112148993792</v>
+        <v>16.62158510088837</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.339157069561854</v>
+        <v>2.303591934923635</v>
       </c>
       <c r="C11" t="n">
-        <v>8.456296439608067</v>
+        <v>9.090951746986846</v>
       </c>
       <c r="D11" t="n">
-        <v>6.342636565126369</v>
+        <v>7.621022207958592</v>
       </c>
       <c r="E11" t="n">
-        <v>17.13809007429629</v>
+        <v>19.01556588986907</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.724069227711371</v>
+        <v>2.670782003319277</v>
       </c>
       <c r="C12" t="n">
-        <v>9.900833801469986</v>
+        <v>10.55079712117756</v>
       </c>
       <c r="D12" t="n">
-        <v>6.722834178802011</v>
+        <v>8.215140338668883</v>
       </c>
       <c r="E12" t="n">
-        <v>19.34773720798337</v>
+        <v>21.43671946316572</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.126152997177254</v>
+        <v>3.014420022513538</v>
       </c>
       <c r="C13" t="n">
-        <v>11.39360945622985</v>
+        <v>12.04967794670272</v>
       </c>
       <c r="D13" t="n">
-        <v>7.06647347955</v>
+        <v>8.707742598183483</v>
       </c>
       <c r="E13" t="n">
-        <v>21.58623593295711</v>
+        <v>23.77184056739974</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.811746665848191</v>
+        <v>1.723605356960912</v>
       </c>
       <c r="C14" t="n">
-        <v>8.095305037155391</v>
+        <v>8.469252737703002</v>
       </c>
       <c r="D14" t="n">
-        <v>5.402999402937108</v>
+        <v>6.575127621991461</v>
       </c>
       <c r="E14" t="n">
-        <v>15.31005110594069</v>
+        <v>16.76798571665537</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.890983523057952</v>
+        <v>1.776227033908542</v>
       </c>
       <c r="C15" t="n">
-        <v>8.728964275384453</v>
+        <v>9.077494527869113</v>
       </c>
       <c r="D15" t="n">
-        <v>5.330359890299887</v>
+        <v>6.625942883163274</v>
       </c>
       <c r="E15" t="n">
-        <v>15.95030768874229</v>
+        <v>17.47966444494093</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.244235982000038</v>
+        <v>2.065017938589783</v>
       </c>
       <c r="C16" t="n">
-        <v>10.35880290911275</v>
+        <v>10.68054126674852</v>
       </c>
       <c r="D16" t="n">
-        <v>5.741054407417455</v>
+        <v>7.109649977045678</v>
       </c>
       <c r="E16" t="n">
-        <v>18.34409329853024</v>
+        <v>19.85520918238398</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.833197853185984</v>
+        <v>1.665593885116969</v>
       </c>
       <c r="C17" t="n">
-        <v>9.609425068984121</v>
+        <v>9.791215291379503</v>
       </c>
       <c r="D17" t="n">
-        <v>5.275097312027834</v>
+        <v>6.613955743694421</v>
       </c>
       <c r="E17" t="n">
-        <v>16.71772023419794</v>
+        <v>18.07076492019089</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.139807478699306</v>
+        <v>1.909901801318788</v>
       </c>
       <c r="C18" t="n">
-        <v>11.28531748751864</v>
+        <v>11.38729162155875</v>
       </c>
       <c r="D18" t="n">
-        <v>5.630205274130947</v>
+        <v>7.113302078505478</v>
       </c>
       <c r="E18" t="n">
-        <v>19.05533024034889</v>
+        <v>20.41049550138302</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.188983221205028</v>
+        <v>1.925570494678567</v>
       </c>
       <c r="C19" t="n">
-        <v>12.1496874362457</v>
+        <v>12.14690909024268</v>
       </c>
       <c r="D19" t="n">
-        <v>5.683622166719017</v>
+        <v>7.243707626060581</v>
       </c>
       <c r="E19" t="n">
-        <v>20.02229282416975</v>
+        <v>21.31618721098183</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.48178947399664</v>
+        <v>2.150429988859256</v>
       </c>
       <c r="C20" t="n">
-        <v>14.00141086861082</v>
+        <v>13.9189244265</v>
       </c>
       <c r="D20" t="n">
-        <v>6.030198741272225</v>
+        <v>7.705354849028558</v>
       </c>
       <c r="E20" t="n">
-        <v>22.51339908387969</v>
+        <v>23.77470926438782</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.498392433606694</v>
+        <v>1.282250859039717</v>
       </c>
       <c r="C21" t="n">
-        <v>10.32533512987498</v>
+        <v>10.21112841943995</v>
       </c>
       <c r="D21" t="n">
-        <v>4.996084614480891</v>
+        <v>6.443485072329006</v>
       </c>
       <c r="E21" t="n">
-        <v>16.81981217796256</v>
+        <v>17.93686435080867</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_65_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_65_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.260491830194688</v>
+        <v>1.255259114931053</v>
       </c>
       <c r="C3" t="n">
-        <v>4.655523099171763</v>
+        <v>4.623253052133171</v>
       </c>
       <c r="D3" t="n">
-        <v>6.136762639764336</v>
+        <v>6.062945029882018</v>
       </c>
       <c r="E3" t="n">
-        <v>12.05277756913079</v>
+        <v>11.94145719694624</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.39971542628037</v>
+        <v>1.380050480876325</v>
       </c>
       <c r="C4" t="n">
-        <v>5.189773612506341</v>
+        <v>5.099984766228042</v>
       </c>
       <c r="D4" t="n">
-        <v>6.494765615580308</v>
+        <v>6.282229301683927</v>
       </c>
       <c r="E4" t="n">
-        <v>13.08425465436702</v>
+        <v>12.76226454878829</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.581422283707176</v>
+        <v>1.549313797143381</v>
       </c>
       <c r="C5" t="n">
-        <v>5.876056195361458</v>
+        <v>5.737494070847093</v>
       </c>
       <c r="D5" t="n">
-        <v>6.904081517466873</v>
+        <v>6.678365745862763</v>
       </c>
       <c r="E5" t="n">
-        <v>14.36155999653551</v>
+        <v>13.96517361385324</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.789226464262463</v>
+        <v>1.754060402787311</v>
       </c>
       <c r="C6" t="n">
-        <v>6.693328845174273</v>
+        <v>6.521432556269497</v>
       </c>
       <c r="D6" t="n">
-        <v>7.273798465883169</v>
+        <v>6.999102609916574</v>
       </c>
       <c r="E6" t="n">
-        <v>15.7563537753199</v>
+        <v>15.27459556897338</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.026038005883567</v>
+        <v>1.987741118300205</v>
       </c>
       <c r="C7" t="n">
-        <v>7.61102783872133</v>
+        <v>7.44113042182846</v>
       </c>
       <c r="D7" t="n">
-        <v>7.713348031550935</v>
+        <v>7.391458403032555</v>
       </c>
       <c r="E7" t="n">
-        <v>17.35041387615583</v>
+        <v>16.82032994316122</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.246807888198828</v>
+        <v>1.241407690035609</v>
       </c>
       <c r="C8" t="n">
-        <v>5.200951611456753</v>
+        <v>5.143156768250938</v>
       </c>
       <c r="D8" t="n">
-        <v>5.95223330032561</v>
+        <v>5.661746979487818</v>
       </c>
       <c r="E8" t="n">
-        <v>12.39999279998119</v>
+        <v>12.04631143777437</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.581970687095269</v>
+        <v>1.563784258529381</v>
       </c>
       <c r="C9" t="n">
-        <v>6.363460991493074</v>
+        <v>6.339176584121261</v>
       </c>
       <c r="D9" t="n">
-        <v>6.495953677582749</v>
+        <v>6.125423723264861</v>
       </c>
       <c r="E9" t="n">
-        <v>14.44138535617109</v>
+        <v>14.0283845659155</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.930079525920942</v>
+        <v>1.895772683242907</v>
       </c>
       <c r="C10" t="n">
-        <v>7.671113641071977</v>
+        <v>7.735500156467296</v>
       </c>
       <c r="D10" t="n">
-        <v>7.020391933895457</v>
+        <v>6.616958123057647</v>
       </c>
       <c r="E10" t="n">
-        <v>16.62158510088837</v>
+        <v>16.24823096276785</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.303591934923635</v>
+        <v>2.221017494740471</v>
       </c>
       <c r="C11" t="n">
-        <v>9.090951746986846</v>
+        <v>9.217217428343677</v>
       </c>
       <c r="D11" t="n">
-        <v>7.621022207958592</v>
+        <v>7.116626348358084</v>
       </c>
       <c r="E11" t="n">
-        <v>19.01556588986907</v>
+        <v>18.55486127144223</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.670782003319277</v>
+        <v>2.558902853283039</v>
       </c>
       <c r="C12" t="n">
-        <v>10.55079712117756</v>
+        <v>10.75452730618029</v>
       </c>
       <c r="D12" t="n">
-        <v>8.215140338668883</v>
+        <v>7.693982582010646</v>
       </c>
       <c r="E12" t="n">
-        <v>21.43671946316572</v>
+        <v>21.00741274147397</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.014420022513538</v>
+        <v>2.879701948712822</v>
       </c>
       <c r="C13" t="n">
-        <v>12.04967794670272</v>
+        <v>12.28017091461236</v>
       </c>
       <c r="D13" t="n">
-        <v>8.707742598183483</v>
+        <v>8.173960638823759</v>
       </c>
       <c r="E13" t="n">
-        <v>23.77184056739974</v>
+        <v>23.33383350214894</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.723605356960912</v>
+        <v>1.660910948567712</v>
       </c>
       <c r="C14" t="n">
-        <v>8.469252737703002</v>
+        <v>8.531848971325777</v>
       </c>
       <c r="D14" t="n">
-        <v>6.575127621991461</v>
+        <v>6.212725274445793</v>
       </c>
       <c r="E14" t="n">
-        <v>16.76798571665537</v>
+        <v>16.40548519433928</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.776227033908542</v>
+        <v>1.696361858168064</v>
       </c>
       <c r="C15" t="n">
-        <v>9.077494527869113</v>
+        <v>9.124176631206048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.625942883163274</v>
+        <v>6.247970017028254</v>
       </c>
       <c r="E15" t="n">
-        <v>17.47966444494093</v>
+        <v>17.06850850640237</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.065017938589783</v>
+        <v>1.964378981427443</v>
       </c>
       <c r="C16" t="n">
-        <v>10.68054126674852</v>
+        <v>10.67122448103521</v>
       </c>
       <c r="D16" t="n">
-        <v>7.109649977045678</v>
+        <v>6.710461543021884</v>
       </c>
       <c r="E16" t="n">
-        <v>19.85520918238398</v>
+        <v>19.34606500548454</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.665593885116969</v>
+        <v>1.569794944136565</v>
       </c>
       <c r="C17" t="n">
-        <v>9.791215291379503</v>
+        <v>9.72768639743769</v>
       </c>
       <c r="D17" t="n">
-        <v>6.613955743694421</v>
+        <v>6.240597091769361</v>
       </c>
       <c r="E17" t="n">
-        <v>18.07076492019089</v>
+        <v>17.53807843334362</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.909901801318788</v>
+        <v>1.79121832135239</v>
       </c>
       <c r="C18" t="n">
-        <v>11.38729162155875</v>
+        <v>11.24539962586396</v>
       </c>
       <c r="D18" t="n">
-        <v>7.113302078505478</v>
+        <v>6.707712649449991</v>
       </c>
       <c r="E18" t="n">
-        <v>20.41049550138302</v>
+        <v>19.74433059666634</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.925570494678567</v>
+        <v>1.801291052797963</v>
       </c>
       <c r="C19" t="n">
-        <v>12.14690909024268</v>
+        <v>11.92443524298331</v>
       </c>
       <c r="D19" t="n">
-        <v>7.243707626060581</v>
+        <v>6.828457799595308</v>
       </c>
       <c r="E19" t="n">
-        <v>21.31618721098183</v>
+        <v>20.55418409537658</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.150429988859256</v>
+        <v>2.018532184793697</v>
       </c>
       <c r="C20" t="n">
-        <v>13.9189244265</v>
+        <v>13.59107959814382</v>
       </c>
       <c r="D20" t="n">
-        <v>7.705354849028558</v>
+        <v>7.385953050928902</v>
       </c>
       <c r="E20" t="n">
-        <v>23.77470926438782</v>
+        <v>22.99556483386642</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.282250859039717</v>
+        <v>1.209640798833623</v>
       </c>
       <c r="C21" t="n">
-        <v>10.21112841943995</v>
+        <v>9.899992937010047</v>
       </c>
       <c r="D21" t="n">
-        <v>6.443485072329006</v>
+        <v>6.194513854532016</v>
       </c>
       <c r="E21" t="n">
-        <v>17.93686435080867</v>
+        <v>17.30414759037568</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_65_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_65_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.255259114931053</v>
+        <v>2.628197031014496</v>
       </c>
       <c r="C3" t="n">
-        <v>4.623253052133171</v>
+        <v>7.718566342484226</v>
       </c>
       <c r="D3" t="n">
-        <v>6.062945029882018</v>
+        <v>8.258390770842293</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94145719694624</v>
+        <v>18.60515414434101</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.380050480876325</v>
+        <v>1.164635749219156</v>
       </c>
       <c r="C4" t="n">
-        <v>5.099984766228042</v>
+        <v>4.561611770874033</v>
       </c>
       <c r="D4" t="n">
-        <v>6.282229301683927</v>
+        <v>5.867738361018208</v>
       </c>
       <c r="E4" t="n">
-        <v>12.76226454878829</v>
+        <v>11.5939858811114</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.549313797143381</v>
+        <v>1.341597620097711</v>
       </c>
       <c r="C5" t="n">
-        <v>5.737494070847093</v>
+        <v>5.28388513941698</v>
       </c>
       <c r="D5" t="n">
-        <v>6.678365745862763</v>
+        <v>6.153777113008299</v>
       </c>
       <c r="E5" t="n">
-        <v>13.96517361385324</v>
+        <v>12.77925987252299</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.754060402787311</v>
+        <v>1.534506110364185</v>
       </c>
       <c r="C6" t="n">
-        <v>6.521432556269497</v>
+        <v>6.196328966561906</v>
       </c>
       <c r="D6" t="n">
-        <v>6.999102609916574</v>
+        <v>6.577427380564787</v>
       </c>
       <c r="E6" t="n">
-        <v>15.27459556897338</v>
+        <v>14.30826245749088</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.987741118300205</v>
+        <v>1.721248589597164</v>
       </c>
       <c r="C7" t="n">
-        <v>7.44113042182846</v>
+        <v>7.258319677832693</v>
       </c>
       <c r="D7" t="n">
-        <v>7.391458403032555</v>
+        <v>6.985662872034117</v>
       </c>
       <c r="E7" t="n">
-        <v>16.82032994316122</v>
+        <v>15.96523113946398</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.241407690035609</v>
+        <v>1.903715830965368</v>
       </c>
       <c r="C8" t="n">
-        <v>5.143156768250938</v>
+        <v>8.4864687600056</v>
       </c>
       <c r="D8" t="n">
-        <v>5.661746979487818</v>
+        <v>7.498399738649903</v>
       </c>
       <c r="E8" t="n">
-        <v>12.04631143777437</v>
+        <v>17.88858432962087</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.563784258529381</v>
+        <v>2.065459368529929</v>
       </c>
       <c r="C9" t="n">
-        <v>6.339176584121261</v>
+        <v>9.847454613820162</v>
       </c>
       <c r="D9" t="n">
-        <v>6.125423723264861</v>
+        <v>8.072405664995804</v>
       </c>
       <c r="E9" t="n">
-        <v>14.0283845659155</v>
+        <v>19.98531964734589</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.895772683242907</v>
+        <v>1.244473207380299</v>
       </c>
       <c r="C10" t="n">
-        <v>7.735500156467296</v>
+        <v>7.214255194933177</v>
       </c>
       <c r="D10" t="n">
-        <v>6.616958123057647</v>
+        <v>6.364523104476436</v>
       </c>
       <c r="E10" t="n">
-        <v>16.24823096276785</v>
+        <v>14.82325150678991</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.221017494740471</v>
+        <v>1.182416934994859</v>
       </c>
       <c r="C11" t="n">
-        <v>9.217217428343677</v>
+        <v>7.758290685241547</v>
       </c>
       <c r="D11" t="n">
-        <v>7.116626348358084</v>
+        <v>6.305883314101773</v>
       </c>
       <c r="E11" t="n">
-        <v>18.55486127144223</v>
+        <v>15.24659093433818</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.558902853283039</v>
+        <v>1.284243806879338</v>
       </c>
       <c r="C12" t="n">
-        <v>10.75452730618029</v>
+        <v>9.266166801671266</v>
       </c>
       <c r="D12" t="n">
-        <v>7.693982582010646</v>
+        <v>6.787185126108772</v>
       </c>
       <c r="E12" t="n">
-        <v>21.00741274147397</v>
+        <v>17.33759573465938</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.879701948712822</v>
+        <v>1.008510146664578</v>
       </c>
       <c r="C13" t="n">
-        <v>12.28017091461236</v>
+        <v>8.895507955932882</v>
       </c>
       <c r="D13" t="n">
-        <v>8.173960638823759</v>
+        <v>6.274261220547983</v>
       </c>
       <c r="E13" t="n">
-        <v>23.33383350214894</v>
+        <v>16.17827932314544</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.660910948567712</v>
+        <v>1.093274243449248</v>
       </c>
       <c r="C14" t="n">
-        <v>8.531848971325777</v>
+        <v>10.4982798054551</v>
       </c>
       <c r="D14" t="n">
-        <v>6.212725274445793</v>
+        <v>6.721339307584938</v>
       </c>
       <c r="E14" t="n">
-        <v>16.40548519433928</v>
+        <v>18.31289335648928</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.696361858168064</v>
+        <v>1.057852786280023</v>
       </c>
       <c r="C15" t="n">
-        <v>9.124176631206048</v>
+        <v>11.40927295265684</v>
       </c>
       <c r="D15" t="n">
-        <v>6.247970017028254</v>
+        <v>6.830499834820141</v>
       </c>
       <c r="E15" t="n">
-        <v>17.06850850640237</v>
+        <v>19.297625573757</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.964378981427443</v>
+        <v>1.159267324128719</v>
       </c>
       <c r="C16" t="n">
-        <v>10.67122448103521</v>
+        <v>13.31307810073225</v>
       </c>
       <c r="D16" t="n">
-        <v>6.710461543021884</v>
+        <v>7.311546392424036</v>
       </c>
       <c r="E16" t="n">
-        <v>19.34606500548454</v>
+        <v>21.78389181728501</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.569794944136565</v>
+        <v>0.6931138791982483</v>
       </c>
       <c r="C17" t="n">
-        <v>9.72768639743769</v>
+        <v>9.977541188168503</v>
       </c>
       <c r="D17" t="n">
-        <v>6.240597091769361</v>
+        <v>6.12607622206897</v>
       </c>
       <c r="E17" t="n">
-        <v>17.53807843334362</v>
+        <v>16.79673128943572</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.79121832135239</v>
+        <v>0.557897767892335</v>
       </c>
       <c r="C18" t="n">
-        <v>11.24539962586396</v>
+        <v>9.016154931307772</v>
       </c>
       <c r="D18" t="n">
-        <v>6.707712649449991</v>
+        <v>5.664173744697888</v>
       </c>
       <c r="E18" t="n">
-        <v>19.74433059666634</v>
+        <v>15.23822644389799</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.801291052797963</v>
+        <v>0.6525775164898975</v>
       </c>
       <c r="C19" t="n">
-        <v>11.92443524298331</v>
+        <v>11.15464686808339</v>
       </c>
       <c r="D19" t="n">
-        <v>6.828457799595308</v>
+        <v>6.28530588222076</v>
       </c>
       <c r="E19" t="n">
-        <v>20.55418409537658</v>
+        <v>18.09253026679405</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.018532184793697</v>
+        <v>0.7414060487701488</v>
       </c>
       <c r="C20" t="n">
-        <v>13.59107959814382</v>
+        <v>13.43101545244342</v>
       </c>
       <c r="D20" t="n">
-        <v>7.385953050928902</v>
+        <v>6.899595238245032</v>
       </c>
       <c r="E20" t="n">
-        <v>22.99556483386642</v>
+        <v>21.0720167394586</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.209640798833623</v>
+        <v>0.8212712245106267</v>
       </c>
       <c r="C21" t="n">
-        <v>9.899992937010047</v>
+        <v>15.72337670690564</v>
       </c>
       <c r="D21" t="n">
-        <v>6.194513854532016</v>
+        <v>7.425154236759477</v>
       </c>
       <c r="E21" t="n">
-        <v>17.30414759037568</v>
+        <v>23.96980216817575</v>
       </c>
     </row>
   </sheetData>
